--- a/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
+++ b/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
@@ -6289,6 +6289,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J132" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7507,5 +7510,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M86" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
+++ b/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="149">
   <si>
     <r>
       <rPr>
@@ -5375,7 +5375,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5514,6 +5514,18 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5967,13 +5979,13 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>35</v>
+      <c r="A48" s="35">
+        <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30" t="s">
-        <v>36</v>
+      <c r="A49" s="36">
+        <v>2</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6338,14 +6350,14 @@
       <c r="B4" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>83</v>
+      <c r="C4" s="37">
+        <v>3</v>
+      </c>
+      <c r="D4" s="37">
+        <v>4</v>
+      </c>
+      <c r="E4" s="37">
+        <v>5</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>84</v>
@@ -7184,14 +7196,14 @@
       <c r="A50" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>129</v>
+      <c r="B50" s="37">
+        <v>5</v>
+      </c>
+      <c r="C50" s="37">
+        <v>4</v>
+      </c>
+      <c r="D50" s="37">
+        <v>3</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>111</v>

--- a/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
+++ b/从零开始学Slots/从零开始学Slots-38-数值篇-SuperStack.xlsx
@@ -5184,7 +5184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00E+00"/>
@@ -5192,6 +5192,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000000%"/>
     <numFmt numFmtId="170" formatCode="0.0000%"/>
+    <numFmt numFmtId="171" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -5375,7 +5376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5526,6 +5527,26 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6812,7 +6833,7 @@
       <c r="E29" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F29" s="23" t="n">
+      <c r="F29" s="39" t="n">
         <f aca="false">SUM(B29:E29)</f>
         <v>1</v>
       </c>
@@ -6834,7 +6855,7 @@
       <c r="E30" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="39" t="n">
         <f aca="false">SUM(B30:E30)</f>
         <v>1</v>
       </c>
@@ -6856,7 +6877,7 @@
       <c r="E31" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F31" s="23" t="n">
+      <c r="F31" s="39" t="n">
         <f aca="false">SUM(B31:E31)</f>
         <v>1</v>
       </c>
@@ -6878,7 +6899,7 @@
       <c r="E32" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F32" s="23" t="n">
+      <c r="F32" s="39" t="n">
         <f aca="false">SUM(B32:E32)</f>
         <v>1</v>
       </c>
@@ -6900,7 +6921,7 @@
       <c r="E33" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="39" t="n">
         <f aca="false">SUM(B33:E33)</f>
         <v>1</v>
       </c>
@@ -7235,11 +7256,11 @@
         <f aca="false">$B$24^5</f>
         <v>10000000000</v>
       </c>
-      <c r="F51" s="26" t="n">
+      <c r="F51" s="40" t="n">
         <f aca="false">IF($B$24^5&lt;=0,0,(B51+C51+D51)/$B$24^5)</f>
         <v>0.009595703125</v>
       </c>
-      <c r="G51" s="27" t="n">
+      <c r="G51" s="41" t="n">
         <f aca="false">(B51/$B$24^5)*100+(C51/$B$24^5)*25+(D51/$B$24^5)*5</f>
         <v>0.121258201599121</v>
       </c>
@@ -7264,11 +7285,11 @@
         <f aca="false">$B$24^5</f>
         <v>10000000000</v>
       </c>
-      <c r="F52" s="26" t="n">
+      <c r="F52" s="40" t="n">
         <f aca="false">IF($B$24^5&lt;=0,0,(B52+C52+D52)/$B$24^5)</f>
         <v>0.030517578125</v>
       </c>
-      <c r="G52" s="27" t="n">
+      <c r="G52" s="41" t="n">
         <f aca="false">(B52/$B$24^5)*50+(C52/$B$24^5)*13+(D52/$B$24^5)*3</f>
         <v>0.297188758850098</v>
       </c>
@@ -7293,11 +7314,11 @@
         <f aca="false">$B$24^5</f>
         <v>10000000000</v>
       </c>
-      <c r="F53" s="26" t="n">
+      <c r="F53" s="40" t="n">
         <f aca="false">IF($B$24^5&lt;=0,0,(B53+C53+D53)/$B$24^5)</f>
         <v>0.030517578125</v>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="41" t="n">
         <f aca="false">(B53/$B$24^5)*38+(C53/$B$24^5)*10+(D53/$B$24^5)*3</f>
         <v>0.241756439208984</v>
       </c>
@@ -7322,11 +7343,11 @@
         <f aca="false">$B$24^5</f>
         <v>10000000000</v>
       </c>
-      <c r="F54" s="26" t="n">
+      <c r="F54" s="40" t="n">
         <f aca="false">IF($B$24^5&lt;=0,0,(B54+C54+D54)/$B$24^5)</f>
         <v>0.030517578125</v>
       </c>
-      <c r="G54" s="27" t="n">
+      <c r="G54" s="41" t="n">
         <f aca="false">(B54/$B$24^5)*25+(C54/$B$24^5)*8+(D54/$B$24^5)*3</f>
         <v>0.189900398254395</v>
       </c>
@@ -7339,11 +7360,11 @@
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="26" t="n">
+      <c r="F55" s="40" t="n">
         <f aca="false">IF($B$24^5&lt;=0,0,SUM(F51:F54))</f>
         <v>0.1011484375</v>
       </c>
-      <c r="G55" s="28" t="n">
+      <c r="G55" s="42" t="n">
         <f aca="false">SUM(G51:G54)</f>
         <v>0.850103797912598</v>
       </c>
